--- a/data/processed/summary_stats.xlsx
+++ b/data/processed/summary_stats.xlsx
@@ -2296,7 +2296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3316,37 +3316,74 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>private_credit_pct_gdp</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>357</v>
+      </c>
+      <c r="C28" t="n">
+        <v>7.633</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4320</v>
+      </c>
+      <c r="E28" t="n">
+        <v>58.574</v>
+      </c>
+      <c r="F28" t="n">
+        <v>40.662</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.441</v>
+      </c>
+      <c r="H28" t="n">
+        <v>30.015</v>
+      </c>
+      <c r="I28" t="n">
+        <v>45.628</v>
+      </c>
+      <c r="J28" t="n">
+        <v>69.283</v>
+      </c>
+      <c r="K28" t="n">
+        <v>194.313</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
           <t>renewable_energy_consumption_pct</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B29" t="n">
         <v>448</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C29" t="n">
         <v>9.579000000000001</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D29" t="n">
         <v>4229</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E29" t="n">
         <v>32.477</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F29" t="n">
         <v>20.698</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G29" t="n">
         <v>0.2</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H29" t="n">
         <v>12.6</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I29" t="n">
         <v>33.4</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J29" t="n">
         <v>44.9</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K29" t="n">
         <v>96.3</v>
       </c>
     </row>
